--- a/src/main/java/UploadDownload/download.xlsx
+++ b/src/main/java/UploadDownload/download.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Documents-Local/Documents/Development_Local/CICD/Introduction/src/main/java/UploadDownload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B86D6A-6751-4544-81E8-622896E4FCEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1B38C2-66F6-3743-89BE-C28D249C4559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24860" yWindow="10880" windowWidth="24280" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6040" yWindow="8980" windowWidth="24280" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Excel" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>

--- a/src/main/java/UploadDownload/download.xlsx
+++ b/src/main/java/UploadDownload/download.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1B38C2-66F6-3743-89BE-C28D249C4559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6040" yWindow="8980" windowWidth="24280" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5180" yWindow="660" windowWidth="24200" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Excel" sheetId="1" r:id="rId1"/>

--- a/src/main/java/UploadDownload/download.xlsx
+++ b/src/main/java/UploadDownload/download.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Documents-Local/Documents/Development_Local/CICD/Introduction/src/main/java/UploadDownload/"/>
     </mc:Choice>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
   <si>
     <t>sno</t>
   </si>
@@ -74,12 +74,16 @@
   </si>
   <si>
     <t>Green</t>
+  </si>
+  <si>
+    <t>598</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -475,7 +479,7 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="16384" style="2" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -526,7 +530,7 @@
         <v>345</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">

--- a/src/main/java/UploadDownload/download.xlsx
+++ b/src/main/java/UploadDownload/download.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mrinmoy/Documents-Local/Documents/Development_Local/CICD/Introduction/src/main/java/UploadDownload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1B38C2-66F6-3743-89BE-C28D249C4559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B971C200-2044-8147-A37E-71A24FDF228B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="660" windowWidth="24200" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7360" yWindow="3840" windowWidth="24200" windowHeight="15120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Excel" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>sno</t>
   </si>
@@ -509,11 +509,11 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1">
-        <v>999</v>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -526,11 +526,11 @@
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1">
-        <v>345</v>
+      <c r="D3" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -604,7 +604,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E1 A3:E7 A2:C2 E2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1 A4:D7 A2:C2 A3:C3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/main/java/UploadDownload/download.xlsx
+++ b/src/main/java/UploadDownload/download.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>sno</t>
   </si>

--- a/src/main/java/UploadDownload/download.xlsx
+++ b/src/main/java/UploadDownload/download.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>sno</t>
   </si>
